--- a/00 포트폴리오/포트폴리오기획서-정재녕(링티).xlsx
+++ b/00 포트폴리오/포트폴리오기획서-정재녕(링티).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>과정명</t>
   </si>
@@ -89,6 +89,54 @@
   </si>
   <si>
     <t>https://positivehotel.com/</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://brand.naver.com/donga-otsuka</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>커뮤니티</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄생스토리 / 연혁 / 활동</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞춤링티</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품소개</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>링티스토리</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>수분건강라인 / 생활건강라인</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">브랜드 정체성 강화
+컨셉과 디자인 일치 :  링티제품의 고객맞춤 과정을 시각적으로 표현
+1.UX 개선 
+건강 설문 과정을 단계별로 시각화
+사용자가 현재 위치와 다음 단계를 쉽게 인지하도록 구성
+2. 맞춤 구매 방식의 의도 제시 
+- 한눈에 볼 수 있는 제품 소개 기능 추가
+3.사용자 흐름 정비 
+로그인/회원가입/마이페이지/섭취기록 구조 통합 </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>베스트 제품 소개</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>FAQ</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -272,7 +320,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -288,65 +336,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -532,7 +583,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -541,7 +592,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -860,281 +911,301 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1"/>
     <row r="3" spans="1:8" ht="26.1" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:8" ht="26.1" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="23">
         <v>45878</v>
       </c>
-      <c r="G4" s="7"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:8" ht="26.1" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
     </row>
     <row r="6" spans="1:8" ht="61.9" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="1:8" ht="26.1" customHeight="1">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="26.1" customHeight="1">
-      <c r="A8" s="13"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="3"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24"/>
+      <c r="C8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="26.1" customHeight="1">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="45.95" customHeight="1">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="14" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
     </row>
     <row r="11" spans="1:8" ht="120" customHeight="1">
-      <c r="A11" s="13"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:8" ht="45.95" customHeight="1">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
     </row>
     <row r="13" spans="1:8" ht="26.1" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13" t="s">
+      <c r="E13" s="15"/>
+      <c r="F13" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:8" ht="26.1" customHeight="1">
-      <c r="A14" s="15"/>
-      <c r="B14" s="7" t="s">
+      <c r="A14" s="17"/>
+      <c r="B14" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="1:8" ht="26.1" customHeight="1">
-      <c r="A15" s="14"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="26.1" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A17" s="15"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A18" s="15"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A20" s="15"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="20"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A21" s="14"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="17"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A22" s="15"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A23" s="15"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="20"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" ht="26.1" customHeight="1">
-      <c r="A24" s="14"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="239.45" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
+      <c r="B26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1"/>
     <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1"/>
@@ -1155,6 +1226,45 @@
     <row r="43" ht="20.100000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="A13:A25"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
@@ -1171,51 +1281,13 @@
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A13:A25"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B5:G5"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C7" r:id="rId1"/>
+    <hyperlink ref="C8" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>